--- a/VerveStacks_BIH_grids_kan10/SuppXLS/Scen_TSParameters_ts_12.xlsx
+++ b/VerveStacks_BIH_grids_kan10/SuppXLS/Scen_TSParameters_ts_12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BIH_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{53DFA90E-35A5-4AB8-A7FC-49BD3918997B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1FE866D1-5AFB-4FFB-8A2E-39DADB82021D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -420,7 +420,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>S3aH3,S4aH1,S2aH1,S1aH1,S4aH3,S3aH1,S2aH3,S1aH3</t>
+    <t>S3aH3,S4aH1,S3aH1,S2aH3,S2aH1,S1aH3,S1aH1,S4aH3</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S3aH3,S4aH1,S2aH1,S1aH1,S4aH3,S3aH1,S2aH3,S1aH3</v>
+        <v>S3aH3,S4aH1,S3aH1,S2aH3,S2aH1,S1aH3,S1aH1,S4aH3</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1143,7 +1143,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{494DDAF5-E0C2-4689-A23E-FC9C9B10E01C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AB0F52C-B15A-4C34-B62A-B9FA9CB48751}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1227,7 +1227,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFFCD4A0-CCE7-4BC9-8F58-E649955B2AE7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{076FB1DC-5E98-4811-8A55-3A974B62C597}">
   <dimension ref="B9:J178"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5065,7 +5065,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC7AE2D4-B550-4AE4-9F75-D504432541A2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{350B897C-B77E-4FE2-BCE7-699283D7C191}">
   <dimension ref="B9:BL34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -7724,7 +7724,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{130B9E11-FCA7-489F-B76F-D431D6E11250}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{905D306B-33C4-4BF5-B207-3152DB66782E}">
   <dimension ref="A9:S34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -7843,7 +7843,7 @@
         <v>0.10273972602739725</v>
       </c>
       <c r="D12">
-        <v>0.14672202471222934</v>
+        <v>0.14672202471222937</v>
       </c>
       <c r="E12" t="s">
         <v>54</v>
@@ -7914,7 +7914,7 @@
         <v>43</v>
       </c>
       <c r="R13">
-        <v>0.18556666666666666</v>
+        <v>0.18556666666666669</v>
       </c>
       <c r="S13" t="s">
         <v>133</v>
@@ -8212,7 +8212,7 @@
         <v>0.10388127853881278</v>
       </c>
       <c r="D21">
-        <v>0.1483522694312541</v>
+        <v>0.14835226943125412</v>
       </c>
       <c r="E21" t="s">
         <v>63</v>
